--- a/experiments/results/resnet18/CIFAR-10/ASH/standard/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/ASH/standard/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -566,6 +566,153 @@
         <v>95.95</v>
       </c>
       <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>64.33</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>96.38</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>94.70999999999999</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=90,react_th=None,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>85.53</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>26.74</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=95,react_th=None,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>96.41</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>96.48999999999999</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>95.95</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=85,react_th=None,scale_th=None,type=avg</t>
         </is>
